--- a/out/MLP-Mamba1_repeat_2_000006.xlsx
+++ b/out/MLP-Mamba1_repeat_2_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.599521431067185</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.199521431067184</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7318388020611866</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7318388020611866</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7318388020611866</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003524812174077378</v>
+        <v>-0.0003099645450405078</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4536705733070571</v>
+        <v>0.3989483040809848</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9082001314514829</v>
+        <v>0.7986520321430224</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.104771279911376</v>
+        <v>-0.09213365868504264</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3485468121782732</v>
+        <v>0.3065046808509017</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.599521431067185</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3485468121782732</v>
+        <v>0.3065046808509017</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.199521431067184</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3481619907043292</v>
+        <v>0.306238699260687</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.182254630765782</v>
+        <v>0.8171529687970616</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.715025722716178</v>
+        <v>1.942171779407156</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2262111023613306</v>
+        <v>0.1563530131826889</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.199521431067184</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.983467826764955</v>
+        <v>1.436532362137132</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3962304167512987</v>
+        <v>0.2738669132738679</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.549828320716389</v>
+        <v>1.827990254026327</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2169899570119218</v>
+        <v>0.1499797261508723</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.587236768271876</v>
+        <v>1.853846300874142</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.08962001233302443</v>
+        <v>0.06194361428682092</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.599521431067185</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.549259279785058</v>
+        <v>1.827596971789875</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.111658844695662</v>
+        <v>0.07717642775855121</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.682972587260801</v>
+        <v>1.920017198078106</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.06723304774398013</v>
+        <v>0.0464701785724467</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.705704267098924</v>
+        <v>1.93572895624997</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05111519042814988</v>
+        <v>0.03532982821195138</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.740673486482372</v>
+        <v>1.959899192600551</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02260838174955362</v>
+        <v>0.0156272693526781</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.734729769339986</v>
+        <v>1.955790945221258</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01793992116994978</v>
+        <v>0.01239923769758195</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.747994021660705</v>
+        <v>1.964957641385154</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.008895266776839357</v>
+        <v>0.00614613996746711</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.747830173988194</v>
+        <v>1.964842858803169</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005170468126474953</v>
+        <v>0.003570407716378706</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.74927114255196</v>
+        <v>1.965837196392294</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002581279462864662</v>
+        <v>0.001784158458562168</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.749262922459442</v>
+        <v>1.965829968769236</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001274218432259858</v>
+        <v>0.0008775169858511826</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.599521431067185</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.749225540329769</v>
+        <v>1.965802594144107</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0007359589166944075</v>
+        <v>0.0005089985277970213</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.749425906530845</v>
+        <v>1.965939733813426</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002427486826508818</v>
+        <v>0.0001668616987758369</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.749173731317327</v>
+        <v>1.965764037853174</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001207643042471784</v>
+        <v>8.034006359629965e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.599521431067185</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.749170122927047</v>
+        <v>1.965759995997409</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>6.349349164303817e-05</v>
+        <v>4.147772647206162e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.749176273244891</v>
+        <v>1.965762762930275</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.818252625748566e-05</v>
+        <v>1.870180446963262e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.199521431067184</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.749169100604869</v>
+        <v>1.965756211044546</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.536440521940679e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.749171630600411</v>
+        <v>1.965756589612791</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.749164296206267</v>
+        <v>1.96574992264892</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.74916081098596</v>
+        <v>1.965746060573824</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.749156263673775</v>
+        <v>1.965741513261639</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.749156353618424</v>
+        <v>1.965741603206289</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.599521431067185</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.749155495684839</v>
+        <v>1.965740745272704</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.749155724005874</v>
+        <v>1.965740973593739</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.749154928341663</v>
+        <v>1.965740177929527</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.749154990611035</v>
+        <v>1.9657402401989</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.599521431067185</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.749155018286312</v>
+        <v>1.965740267874177</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>2.199521431067184</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.749155170500335</v>
+        <v>1.9657404200882</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.749154824559374</v>
+        <v>1.965740074147238</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.749154900666385</v>
+        <v>1.96574015025425</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.749155066718047</v>
+        <v>1.965740316305912</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.749155426496647</v>
+        <v>1.965740676084512</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.749155447253105</v>
+        <v>1.965740696840969</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.749155551035393</v>
+        <v>1.965740800623258</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.749155779356428</v>
+        <v>1.965741028944292</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.749155654817682</v>
+        <v>1.965740904405546</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.599521431067185</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.749155682492959</v>
+        <v>1.965740932080823</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.599521431067185</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.749155737843513</v>
+        <v>1.965740987431377</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.749156000758643</v>
+        <v>1.965741250346508</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.749155917732812</v>
+        <v>1.965741167320677</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.599521431067185</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.749155710168235</v>
+        <v>1.9657409597561</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.199521431067184</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.749155724005874</v>
+        <v>1.965740973593739</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.749155862382259</v>
+        <v>1.965741111970123</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.74915557871067</v>
+        <v>1.965740828298535</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.749155405740189</v>
+        <v>1.965740655328054</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.599521431067185</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.749155301957901</v>
+        <v>1.965740551545766</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.749155447253105</v>
+        <v>1.965740696840969</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.749155689411778</v>
+        <v>1.965740938999643</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.749155516441297</v>
+        <v>1.965740766029162</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.74915521893207</v>
+        <v>1.965740468519935</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.749155205094432</v>
+        <v>1.965740454682296</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.749154838397012</v>
+        <v>1.965740087984877</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.749154838397012</v>
+        <v>1.965740087984877</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.749154776127639</v>
+        <v>1.965740025715504</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.74915467234535</v>
+        <v>1.965739921933215</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.74915449937487</v>
+        <v>1.965739748962734</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.749154547806604</v>
+        <v>1.965739797394469</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.749154188028005</v>
+        <v>1.965739437615869</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.749154146515089</v>
+        <v>1.965739396102954</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.749154201865643</v>
+        <v>1.965739451453507</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.749154257216197</v>
+        <v>1.965739506804062</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.749154298729112</v>
+        <v>1.965739548316977</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.749154028895162</v>
+        <v>1.965739278483027</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.749154084245716</v>
+        <v>1.96573933383358</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.74915422954092</v>
+        <v>1.965739479128785</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.749154194946823</v>
+        <v>1.965739444534688</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.749154181109185</v>
+        <v>1.96573943069705</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.749154271053835</v>
+        <v>1.9657395206417</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.199521431067184</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.74915458931952</v>
+        <v>1.965739838907384</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.74915440943022</v>
+        <v>1.965739659018084</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.749154450943135</v>
+        <v>1.965739700531</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.749154264135016</v>
+        <v>1.965739513722881</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.749154333323208</v>
+        <v>1.965739582911073</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.749154132677451</v>
+        <v>1.965739382265315</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.749154174190366</v>
+        <v>1.965739423778231</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.749154201865643</v>
+        <v>1.965739451453507</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_2_000006.xlsx
+++ b/out/MLP-Mamba1_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.07752141098404314</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.331838802061187</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.199521431067184</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.331838802061187</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5475466071276708</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.199521431067184</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5475466071276708</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.199521431067184</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.199521431067184</v>
+        <v>0.122478589015957</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.122478589015957</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.199521431067184</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5475466071276708</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5475466071276708</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003524812174077378</v>
+        <v>-0.0001909708426891593</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4536705733070571</v>
+        <v>0.2457941399915658</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9082001314514829</v>
+        <v>0.4920538626142966</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.104771279911376</v>
+        <v>-0.05676406706592143</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3485468121782732</v>
+        <v>0.1888391020829552</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.599521431067185</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3485468121782732</v>
+        <v>0.1888391020829552</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3481619907043292</v>
+        <v>0.1886408196185769</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.182254630765782</v>
+        <v>0.6091664507148851</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.715025722716178</v>
+        <v>1.408187039015437</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2262111023613306</v>
+        <v>0.116557198564455</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.07752141098404314</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.983467826764955</v>
+        <v>1.03124570119872</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3962304167512987</v>
+        <v>0.2041607698110041</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404314</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.549828320716389</v>
+        <v>1.323067613178134</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2169899570119218</v>
+        <v>0.1118058670805367</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404317</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.587236768271876</v>
+        <v>1.34234264479329</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.08962001233302443</v>
+        <v>0.04617745136523378</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595846</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.549259279785058</v>
+        <v>1.322774390016536</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.111658844695662</v>
+        <v>0.05753314171919754</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.682972587260801</v>
+        <v>1.39167156086779</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.06723304774398013</v>
+        <v>0.03464297359949391</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.705704267098924</v>
+        <v>1.403384342899288</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05111519042814988</v>
+        <v>0.02633707492756113</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.740673486482372</v>
+        <v>1.421402513253103</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02260838174955362</v>
+        <v>0.01164768942470142</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.734729769339986</v>
+        <v>1.418338648155235</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01793992116994978</v>
+        <v>0.009241428507388249</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.747994021660705</v>
+        <v>1.425171393529066</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.008895266776839357</v>
+        <v>0.004580213322638151</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.747830173988194</v>
+        <v>1.42508453809478</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005170468126474953</v>
+        <v>0.002662737083742289</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.74927114255196</v>
+        <v>1.425824874335913</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002581279462864662</v>
+        <v>0.00132741394149833</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.331838802061187</v>
+        <v>0.5925037851595846</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.749262922459442</v>
+        <v>1.42581821539061</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001274218432259858</v>
+        <v>0.0006532944291854099</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.07752141098404314</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.749225540329769</v>
+        <v>1.425796516734278</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0007359589166944075</v>
+        <v>0.0003788300694588147</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404314</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.749425906530845</v>
+        <v>1.425897659993835</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002427486826508818</v>
+        <v>0.0001222222964963988</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404317</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.749173731317327</v>
+        <v>1.425765193635558</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001207643042471784</v>
+        <v>6.012794327086025e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.749170122927047</v>
+        <v>1.425760914290592</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>6.349349164303817e-05</v>
+        <v>2.924674582151908e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.331838802061187</v>
+        <v>0.5925037851595846</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.749176273244891</v>
+        <v>1.425761690095271</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.818252625748566e-05</v>
+        <v>1.159126312874283e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.07752141098404305</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.749169100604869</v>
+        <v>1.425755527668249</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.536440521940679e-05</v>
+        <v>6.636802982518164e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.331838802061187</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.749171630600411</v>
+        <v>1.425754830522846</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.749164296206267</v>
+        <v>1.425748495662298</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.74916081098596</v>
+        <v>1.425744253052144</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.122478589015957</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.749156263673775</v>
+        <v>1.425744481373179</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404303</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.749156353618424</v>
+        <v>1.425744571317829</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.07752141098404303</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.749155495684839</v>
+        <v>1.425743713384244</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404303</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.749155724005874</v>
+        <v>1.425743941705279</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.749154928341663</v>
+        <v>1.425743146041067</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404294</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.749154990611035</v>
+        <v>1.42574320831044</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595847</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.749155018286312</v>
+        <v>1.425743235985717</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.749155170500335</v>
+        <v>1.42574338819974</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.749154824559374</v>
+        <v>1.425743042258779</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.199521431067184</v>
+        <v>0.122478589015957</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.749154900666385</v>
+        <v>1.42574311836579</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.331838802061187</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.749155066718047</v>
+        <v>1.425743284417452</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.749155426496647</v>
+        <v>1.425743644196052</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.749155447253105</v>
+        <v>1.425743664952509</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.749155551035393</v>
+        <v>1.425743768734798</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.749155779356428</v>
+        <v>1.425743997055833</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.331838802061187</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.749155654817682</v>
+        <v>1.425743872517087</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595847</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.749155682492959</v>
+        <v>1.425743900192364</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595847</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.749155737843513</v>
+        <v>1.425743955542917</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.331838802061187</v>
+        <v>0.5925037851595847</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.749156000758643</v>
+        <v>1.425744218458048</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595847</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.749155917732812</v>
+        <v>1.425744135432217</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.599521431067185</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.749155710168235</v>
+        <v>1.42574392786764</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.749155724005874</v>
+        <v>1.425743941705279</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404303</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.749155862382259</v>
+        <v>1.425744080081664</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.74915557871067</v>
+        <v>1.425743796410075</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404294</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.749155405740189</v>
+        <v>1.425743623439594</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595847</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.749155301957901</v>
+        <v>1.425743519657306</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.199521431067184</v>
+        <v>0.5925037851595847</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.749155447253105</v>
+        <v>1.425743664952509</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.122478589015957</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.749155689411778</v>
+        <v>1.425743907111183</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.749155516441297</v>
+        <v>1.425743734140702</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.74915521893207</v>
+        <v>1.425743436631475</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.749155205094432</v>
+        <v>1.425743422793836</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404294</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.749154838397012</v>
+        <v>1.425743056096417</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.077521410984043</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.749154838397012</v>
+        <v>1.425743056096417</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.122478589015957</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.749154776127639</v>
+        <v>1.425742993827044</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.74915467234535</v>
+        <v>1.425742890044755</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.74915449937487</v>
+        <v>1.425742717074274</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.749154547806604</v>
+        <v>1.425742765506009</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.749154188028005</v>
+        <v>1.425742405727409</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.749154146515089</v>
+        <v>1.425742364214494</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.749154201865643</v>
+        <v>1.425742419565048</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.749154257216197</v>
+        <v>1.425742474915602</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.749154298729112</v>
+        <v>1.425742516428517</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.749154028895162</v>
+        <v>1.425742246594567</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.749154084245716</v>
+        <v>1.425742301945121</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.74915422954092</v>
+        <v>1.425742447240325</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.749154194946823</v>
+        <v>1.425742412646228</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.331838802061187</v>
+        <v>0.1224785890159571</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.749154181109185</v>
+        <v>1.42574239880859</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.749154271053835</v>
+        <v>1.42574248875324</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.199521431067184</v>
+        <v>0.792503785159585</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.74915458931952</v>
+        <v>1.425742807018924</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159571</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.74915440943022</v>
+        <v>1.425742627129625</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5475466071276708</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.749154450943135</v>
+        <v>1.42574266864254</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.749154264135016</v>
+        <v>1.425742481834421</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.749154333323208</v>
+        <v>1.425742551022613</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.749154132677451</v>
+        <v>1.425742350376856</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.749154174190366</v>
+        <v>1.425742391889771</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.749154201865643</v>
+        <v>1.425742419565048</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_2_000006.xlsx
+++ b/out/MLP-Mamba1_repeat_2_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4913532137870789</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.02000000000000013</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4856769740581512</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.09000000000000008</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4906509816646576</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.0775214109840431</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.51102215051651</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.07752141098404314</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4331831932067871</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.5031363964080811</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.1224785890159569</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4399369060993195</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.1224785890159569</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4821748435497284</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.490669310092926</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4221422374248505</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4639486968517303</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.439577728509903</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.5046023726463318</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4222553670406342</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.1224785890159569</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4195491373538971</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5475466071276708</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4197263121604919</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4765801727771759</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4827351272106171</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.0775214109840431</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.5108802318572998</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.1224785890159569</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4446410238742828</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.1224785890159569</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4022864401340485</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.5475466071276708</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4309913218021393</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4242886006832123</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5215610861778259</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.1224785890159569</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4056534767150879</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.5922530889511108</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.122478589015957</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4880394637584686</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.122478589015957</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4701392948627472</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.411732405424118</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4791213572025299</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.3991000950336456</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3839989602565765</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4343240559101105</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5067353248596191</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.1224785890159569</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4252155125141144</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.1224785890159569</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4195440113544464</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5475466071276708</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4864814579486847</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.3899914920330048</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4209586381912231</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4371042847633362</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.0775214109840431</v>
+        <v>0.16</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5271100401878357</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.581193208694458</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.462528981303212</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.5987486839294434</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001909708426891593</v>
+        <v>-0.0001505071560592624</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2457941399915658</v>
+        <v>0.1937144337915407</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>0.4296576380729675</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.1224785890159569</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4920538626142966</v>
+        <v>0.3877954684738684</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05676406706592143</v>
+        <v>-0.04473662505144678</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.2597708702087402</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.1224785890159569</v>
+        <v>0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1888391020829552</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5515873432159424</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1888391020829552</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.5661922693252563</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.7925037851595848</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1886408196185769</v>
+        <v>0.1487414633451898</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.6091664507148851</v>
+        <v>0.2637136339091658</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.3551417887210846</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7925037851595846</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.408187039015437</v>
+        <v>0.6766938466458761</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.116557198564455</v>
+        <v>0.05045857031788842</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.5981248617172241</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.07752141098404314</v>
+        <v>0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.03124570119872</v>
+        <v>0.5135126392995678</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2041607698110041</v>
+        <v>0.08838297130618772</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.4865266084671021</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.07752141098404314</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.323067613178134</v>
+        <v>0.6398450573440544</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1118058670805367</v>
+        <v>0.0484019696582307</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4299639463424683</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.07752141098404317</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.34234264479329</v>
+        <v>0.6481894091249795</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.04617745136523378</v>
+        <v>0.01999052154930155</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.6195612549781799</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5925037851595846</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.322774390016536</v>
+        <v>0.639718136210965</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.05753314171919754</v>
+        <v>0.02490647437945315</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.6638562083244324</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.462528981303212</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.39167156086779</v>
+        <v>0.6695445068397418</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03464297359949391</v>
+        <v>0.01499741439236807</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.6871166229248047</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.462528981303212</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.403384342899288</v>
+        <v>0.6746150692310582</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02633707492756113</v>
+        <v>0.01139986482293197</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.505506694316864</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.462528981303212</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.421402513253103</v>
+        <v>0.6824140553408168</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01164768942470142</v>
+        <v>0.005039413016094149</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.6859493851661682</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.462528981303212</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.418338648155235</v>
+        <v>0.6810847644414517</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.009241428507388249</v>
+        <v>0.003997750147633703</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.6398117542266846</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.462528981303212</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.425171393529066</v>
+        <v>0.6840403328480719</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.004580213322638151</v>
+        <v>0.001981175329064207</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.803977370262146</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.462528981303212</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.42508453809478</v>
+        <v>0.6839998845479104</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002662737083742289</v>
+        <v>0.001149952696014928</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.838050901889801</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.425824874335913</v>
+        <v>0.6843175655596112</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.00132741394149833</v>
+        <v>0.0005710217476346492</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.3047911524772644</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5925037851595846</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.42581821539061</v>
+        <v>0.6843118483736508</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0006532944291854099</v>
+        <v>0.0002795901680757886</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.8050188422203064</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.07752141098404314</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.425796516734278</v>
+        <v>0.6842996096653126</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003788300694588147</v>
+        <v>0.0001618826388951368</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3279553353786469</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.07752141098404314</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.425897659993835</v>
+        <v>0.684340758908598</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001222222964963988</v>
+        <v>5.079925284929769e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4875554442405701</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.07752141098404317</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.425765193635558</v>
+        <v>0.6842803381422825</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>6.012794327086025e-05</v>
+        <v>2.194949376725252e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.5847484469413757</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.425760914290592</v>
+        <v>0.6842756501820041</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.924674582151908e-05</v>
+        <v>9.677176780651038e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.4568295776844025</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.5925037851595846</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.425761690095271</v>
+        <v>0.6842732401815853</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.159126312874283e-05</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.7920011878013611</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.07752141098404305</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.425755527668249</v>
+        <v>0.6842676985088549</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.636802982518164e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4576772153377533</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.7925037851595848</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.425754830522846</v>
+        <v>0.684264849936153</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.7341060042381287</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.425748495662298</v>
+        <v>0.6842591825058794</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.7928723692893982</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.425744253052144</v>
+        <v>0.684259563040937</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.4216644763946533</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.122478589015957</v>
+        <v>0.16</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.425744481373179</v>
+        <v>0.6842597913619718</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.2325160205364227</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.07752141098404303</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.425744571317829</v>
+        <v>0.6842598813066217</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.5263397097587585</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.07752141098404303</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.425743713384244</v>
+        <v>0.6842590233730369</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.2944656312465668</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.07752141098404303</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.425743941705279</v>
+        <v>0.6842592516940715</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4926120638847351</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.425743146041067</v>
+        <v>0.6842584560298598</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.3986257910728455</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.07752141098404294</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.42574320831044</v>
+        <v>0.6842585182992329</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.5197603106498718</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.5925037851595847</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.425743235985717</v>
+        <v>0.6842585459745097</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.5399091839790344</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.7925037851595848</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.42574338819974</v>
+        <v>0.684258698188533</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3876906335353851</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7925037851595848</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.425743042258779</v>
+        <v>0.6842583522475714</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.5904697775840759</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.122478589015957</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.42574311836579</v>
+        <v>0.6842584283545829</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3978492915630341</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.425743284417452</v>
+        <v>0.6842585944062446</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.7299275994300842</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.425743644196052</v>
+        <v>0.6842589541848446</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5839320421218872</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.462528981303212</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.425743664952509</v>
+        <v>0.6842589749413023</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.7501128315925598</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.462528981303212</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.425743768734798</v>
+        <v>0.6842590787235908</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.5055042505264282</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.425743997055833</v>
+        <v>0.6842593070446256</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.4943987429141998</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.425743872517087</v>
+        <v>0.6842591825058794</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.5263143181800842</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.5925037851595847</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.425743900192364</v>
+        <v>0.6842592101811562</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.7306548357009888</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.5925037851595847</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.425743955542917</v>
+        <v>0.6842592655317101</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3313166201114655</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.5925037851595847</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.425744218458048</v>
+        <v>0.6842595284468408</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.5079244375228882</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.5925037851595847</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.425744135432217</v>
+        <v>0.68425944542101</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.5695966482162476</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.462528981303212</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.42574392786764</v>
+        <v>0.6842592378564333</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.5538787841796875</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.425743941705279</v>
+        <v>0.6842592516940715</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.4160629510879517</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.07752141098404303</v>
+        <v>0.16</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.425744080081664</v>
+        <v>0.6842593900704563</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3271580934524536</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.425743796410075</v>
+        <v>0.6842591063988677</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3883774876594543</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.07752141098404294</v>
+        <v>0.16</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.425743623439594</v>
+        <v>0.684258933428387</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.6729862093925476</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.5925037851595847</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.425743519657306</v>
+        <v>0.6842588296460984</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.613164484500885</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.5925037851595847</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.425743664952509</v>
+        <v>0.6842589749413023</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4804007411003113</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.122478589015957</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.425743907111183</v>
+        <v>0.6842592170999756</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.2433290630578995</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.425743734140702</v>
+        <v>0.6842590441294946</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4425314366817474</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.425743436631475</v>
+        <v>0.6842587466202676</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.2293838262557983</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.425743422793836</v>
+        <v>0.6842587327826291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.4178885519504547</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.07752141098404294</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.425743056096417</v>
+        <v>0.6842583660852098</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.5820838212966919</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.077521410984043</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.425743056096417</v>
+        <v>0.6842583660852098</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.2710857093334198</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.122478589015957</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.425742993827044</v>
+        <v>0.6842583038158367</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3454846739768982</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.425742890044755</v>
+        <v>0.6842582000335483</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4079565405845642</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.425742717074274</v>
+        <v>0.6842580270630675</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.2800378203392029</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.425742765506009</v>
+        <v>0.6842580754948021</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.2972925305366516</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.425742405727409</v>
+        <v>0.6842577157162021</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4299548268318176</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.425742364214494</v>
+        <v>0.6842576742032866</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4509178102016449</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.425742419565048</v>
+        <v>0.6842577295538403</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3485863208770752</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.425742474915602</v>
+        <v>0.6842577849043943</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3041230440139771</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.425742516428517</v>
+        <v>0.6842578264173097</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.318906843662262</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.425742246594567</v>
+        <v>0.6842575565833596</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.4765694141387939</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.425742301945121</v>
+        <v>0.6842576119339135</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3408656120300293</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.425742447240325</v>
+        <v>0.6842577572291174</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4244944453239441</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.425742412646228</v>
+        <v>0.6842577226350212</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.327604353427887</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.1224785890159571</v>
+        <v>0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.42574239880859</v>
+        <v>0.6842577087973827</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.6824468374252319</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.42574248875324</v>
+        <v>0.6842577987420329</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.623423159122467</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.792503785159585</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.425742807018924</v>
+        <v>0.6842581170077174</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.27070352435112</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.1224785890159571</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.425742627129625</v>
+        <v>0.6842579371184173</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.3469246327877045</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5475466071276708</v>
+        <v>0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.42574266864254</v>
+        <v>0.6842579786313328</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4648847877979279</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.425742481834421</v>
+        <v>0.6842577918232134</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.2893547415733337</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.425742551022613</v>
+        <v>0.684257861011406</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3890760838985443</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.425742350376856</v>
+        <v>0.6842576603656481</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4024573266506195</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3700000000000002</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.425742391889771</v>
+        <v>0.6842577018785635</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4796760976314545</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.4400000000000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.425742419565048</v>
+        <v>0.6842577295538403</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_2_000006.xlsx
+++ b/out/MLP-Mamba1_repeat_2_000006.xlsx
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.4856769740581512</v>
+        <v>0.4856769144535065</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.09000000000000008</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.4906509816646576</v>
+        <v>0.4906509220600128</v>
       </c>
       <c r="JB4" t="n">
         <v>0.4399999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.4022864401340485</v>
+        <v>0.4022864103317261</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.1199999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.4242886006832123</v>
+        <v>0.4242885410785675</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.7199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.4056534767150879</v>
+        <v>0.4056534469127655</v>
       </c>
       <c r="JB26" t="n">
         <v>0.4399999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.5922530889511108</v>
+        <v>0.5922530293464661</v>
       </c>
       <c r="JB27" t="n">
         <v>0.5799999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.4791213572025299</v>
+        <v>0.4791212975978851</v>
       </c>
       <c r="JB31" t="n">
         <v>0.02000000000000007</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.4195440113544464</v>
+        <v>0.419543981552124</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.4399999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.581193208694458</v>
+        <v>0.5811932682991028</v>
       </c>
       <c r="JB43" t="n">
         <v>0.4399999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.5987486839294434</v>
+        <v>0.5987486243247986</v>
       </c>
       <c r="JB44" t="n">
         <v>0.4399999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.2597708702087402</v>
+        <v>0.2597709000110626</v>
       </c>
       <c r="JB46" t="n">
         <v>0.3</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.3551417887210846</v>
+        <v>0.3551418483257294</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.02000000000000007</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.6638562083244324</v>
+        <v>0.6638561487197876</v>
       </c>
       <c r="JB54" t="n">
         <v>0.7199999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.505506694316864</v>
+        <v>0.5055066347122192</v>
       </c>
       <c r="JB56" t="n">
         <v>0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.6398117542266846</v>
+        <v>0.6398116946220398</v>
       </c>
       <c r="JB58" t="n">
         <v>0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.803977370262146</v>
+        <v>0.8039772510528564</v>
       </c>
       <c r="JB59" t="n">
         <v>0.7199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.3047911524772644</v>
+        <v>0.304791122674942</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.1600000000000001</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.4875554442405701</v>
+        <v>0.4875553250312805</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.5799999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.5847484469413757</v>
+        <v>0.5847483277320862</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.4568295776844025</v>
+        <v>0.4568295180797577</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.4576772153377533</v>
+        <v>0.4576770961284637</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.3</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.7928723692893982</v>
+        <v>0.7928723096847534</v>
       </c>
       <c r="JB70" t="n">
         <v>0.1600000000000001</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.4216644763946533</v>
+        <v>0.4216643869876862</v>
       </c>
       <c r="JB71" t="n">
         <v>0.16</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.2325160205364227</v>
+        <v>0.2325159907341003</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.5263397097587585</v>
+        <v>0.5263396501541138</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.2944656312465668</v>
+        <v>0.2944656014442444</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.3986257910728455</v>
+        <v>0.3986257612705231</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.5197603106498718</v>
+        <v>0.5197602510452271</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.5399091839790344</v>
+        <v>0.5399091243743896</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.7199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.3876906335353851</v>
+        <v>0.3876905739307404</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.7199999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.5904697775840759</v>
+        <v>0.5904697179794312</v>
       </c>
       <c r="JB80" t="n">
         <v>0.1600000000000001</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.3978492915630341</v>
+        <v>0.3978492319583893</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.7299275994300842</v>
+        <v>0.7299275398254395</v>
       </c>
       <c r="JB82" t="n">
         <v>0.7199999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.5839320421218872</v>
+        <v>0.5839319825172424</v>
       </c>
       <c r="JB83" t="n">
         <v>0.4399999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.7501128315925598</v>
+        <v>0.750112771987915</v>
       </c>
       <c r="JB84" t="n">
         <v>0.4399999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.5055042505264282</v>
+        <v>0.5055041313171387</v>
       </c>
       <c r="JB85" t="n">
         <v>0.16</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.4943987429141998</v>
+        <v>0.4943986833095551</v>
       </c>
       <c r="JB86" t="n">
         <v>0.16</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.5263143181800842</v>
+        <v>0.5263141989707947</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.7199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.7306548357009888</v>
+        <v>0.730654776096344</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.7199999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.3313166201114655</v>
+        <v>0.3313165307044983</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.5079244375228882</v>
+        <v>0.5079243779182434</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.1600000000000001</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.5538787841796875</v>
+        <v>0.5538786649703979</v>
       </c>
       <c r="JB92" t="n">
         <v>0.1600000000000001</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.4160629510879517</v>
+        <v>0.4160628616809845</v>
       </c>
       <c r="JB93" t="n">
         <v>0.16</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.3271580934524536</v>
+        <v>0.3271580636501312</v>
       </c>
       <c r="JB94" t="n">
         <v>0.16</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.3883774876594543</v>
+        <v>0.3883773982524872</v>
       </c>
       <c r="JB95" t="n">
         <v>0.16</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.6729862093925476</v>
+        <v>0.6729861497879028</v>
       </c>
       <c r="JB96" t="n">
         <v>0.1600000000000001</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.613164484500885</v>
+        <v>0.6131644248962402</v>
       </c>
       <c r="JB97" t="n">
         <v>0.1600000000000001</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.4804007411003113</v>
+        <v>0.4804006814956665</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.4399999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.2433290630578995</v>
+        <v>0.2433290034532547</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.7199999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.4425314366817474</v>
+        <v>0.4425313174724579</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.2293838262557983</v>
+        <v>0.2293839603662491</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.4178885519504547</v>
+        <v>0.4178886413574219</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.7199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.5820838212966919</v>
+        <v>0.5820837616920471</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.7199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.3454846739768982</v>
+        <v>0.345484733581543</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.7199999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.4079565405845642</v>
+        <v>0.4079566299915314</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.2800378203392029</v>
+        <v>0.28003790974617</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.2972925305366516</v>
+        <v>0.2972926199436188</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.4509178102016449</v>
+        <v>0.4509178996086121</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.3485863208770752</v>
+        <v>0.3485864102840424</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.3041230440139771</v>
+        <v>0.3041231334209442</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.7199999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.318906843662262</v>
+        <v>0.3189069032669067</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.1199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.4765694141387939</v>
+        <v>0.4765694439411163</v>
       </c>
       <c r="JB114" t="n">
         <v>0.02000000000000007</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.3408656120300293</v>
+        <v>0.3408656716346741</v>
       </c>
       <c r="JB115" t="n">
         <v>0.02000000000000007</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.4244944453239441</v>
+        <v>0.4244945049285889</v>
       </c>
       <c r="JB116" t="n">
         <v>0.3</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.327604353427887</v>
+        <v>0.3276044130325317</v>
       </c>
       <c r="JB117" t="n">
         <v>0.3</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.3469246327877045</v>
+        <v>0.3469247221946716</v>
       </c>
       <c r="JB121" t="n">
         <v>0.16</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.4648847877979279</v>
+        <v>0.4648849070072174</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.1199999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.2893547415733337</v>
+        <v>0.2893548309803009</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.5799999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.3890760838985443</v>
+        <v>0.3890761137008667</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.4024573266506195</v>
+        <v>0.4024573564529419</v>
       </c>
       <c r="JB125" t="n">
         <v>0.3700000000000002</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.4796760976314545</v>
+        <v>0.4796761274337769</v>
       </c>
       <c r="JB126" t="n">
         <v>0.4400000000000002</v>
